--- a/data/trans_dic/IP31KM08_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,7; 53,31</t>
+          <t>24,45; 41,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,37; 43,8</t>
+          <t>39,92; 54,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,36; 45,52</t>
+          <t>33,61; 45,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,07; 50,49</t>
+          <t>44,35; 57,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,85; 55,19</t>
+          <t>41,05; 54,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,12; 51,43</t>
+          <t>45,61; 53,82</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 38,08</t>
+          <t>31,91; 46,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,63; 46,64</t>
+          <t>28,68; 41,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 40,7</t>
+          <t>32,46; 42,3</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,62; 61,92</t>
+          <t>48,52; 61,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,86; 60,93</t>
+          <t>48,63; 61,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,85; 59,61</t>
+          <t>49,92; 59,77</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,82; 46,72</t>
+          <t>42,18; 49,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,04; 48,56</t>
+          <t>42,87; 49,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,79; 46,73</t>
+          <t>43,31; 48,52</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>39677</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45523</t>
+          <t>55755</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97375</t>
+          <t>95432</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43075; 60911</t>
+          <t>30048; 50458</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31979; 59932</t>
+          <t>47339; 64978</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81249; 114293</t>
+          <t>81176; 109903</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82570</t>
+          <t>118063</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>120757</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203327</t>
+          <t>203951</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68996; 93968</t>
+          <t>102561; 132027</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106058; 136611</t>
+          <t>74133; 97541</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>182662; 223010</t>
+          <t>187832; 221651</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>65470</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71847</t>
+          <t>54492</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128198</t>
+          <t>119962</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33674; 71683</t>
+          <t>53139; 76984</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57912; 85402</t>
+          <t>44470; 64651</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96751; 151134</t>
+          <t>104373; 136014</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>127</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>91316</t>
+          <t>91055</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95649</t>
+          <t>90821</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186965</t>
+          <t>181875</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79982; 101877</t>
+          <t>80615; 102809</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84864; 108029</t>
+          <t>79739; 101285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170411; 203778</t>
+          <t>164804; 197334</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>406</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>282089</t>
+          <t>314265</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286956</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615865</t>
+          <t>601221</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>240513; 305116</t>
+          <t>289722; 339438</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>305651; 361634</t>
+          <t>265036; 307614</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>570122; 653213</t>
+          <t>565196; 633148</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM08_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman pasta o arroz casi a diario (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>32,29%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47,01%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>24,45; 41,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>39,92; 54,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33,61; 45,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>51,06%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47,56%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>49,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>44,35; 57,1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>41,05; 54,01</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45,61; 53,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>35,15%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>31,91; 46,23</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28,68; 41,7</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32,46; 42,3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>54,8%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>48,52; 61,87</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>48,63; 61,77</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49,92; 59,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>45,76%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>46,42%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>42,18; 49,42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>42,87; 49,76</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43,31; 48,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.3228525846405946</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4701181056550223</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3951746601581559</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>39677</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55755</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95432</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2444960075243529</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3991582766986204</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.3361390812902224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>30048; 50458</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47339; 64978</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>81176; 109903</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.410571148508468</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5478810452000582</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4550978471805954</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5105625331066156</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4755912980886089</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4952273162485641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>118063</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>85888</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>203951</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4435244996391372</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4104974799838242</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4560878959067685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>102561; 132027</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>74133; 97541</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>187832; 221651</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5709518439142659</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.540117683794284</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5382050218587715</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3931620314204617</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3514747436313342</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3730627605454394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>65470</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>54492</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>119962</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.319108446010179</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.2868298632167508</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3245844485518223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>53139; 76984</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>44470; 64651</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>104373; 136014</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4623055789347421</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4169997919814611</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4229815802709447</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5479776487476608</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5538560230532208</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5508973747254619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>91055</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>90821</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>181875</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4851503829083741</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4862772706815428</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4991873156374232</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>80615; 102809</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>79739; 101285</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164804; 197334</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6187176567142435</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6176732917259391</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5977210357688056</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4575627130454269</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4641741812609337</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.460694638106942</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>314265</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>286956</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>601221</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.421827956503055</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4287162446171972</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4330902097975672</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>289722; 339438</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>265036; 307614</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>565196; 633148</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4942146041384561</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4975903179044531</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.4851592107474283</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman pasta o arroz casi a diario (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>39677</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>55755</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>95432</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>30048</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>47339</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>81176</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>50458</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>64978</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>109903</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>149</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>118063</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>85888</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>203951</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>102561</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>74133</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>187832</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>132027</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>97541</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>221651</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>65470</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>54492</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>119962</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>53139</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>44470</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>104373</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>76984</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>64651</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>136014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>91055</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>90821</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>181875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>80615</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>79739</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>164804</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>102809</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>101285</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>197334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>416</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>406</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>314265</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>286956</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>601221</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>289722</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>265036</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>565196</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>339438</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>307614</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>633148</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>